--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-organization-type-activite.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-organization-type-activite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:14:39+00:00</t>
+    <t>2026-09-17T13:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-organization-type-activite.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-organization-type-activite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:19:58+00:00</t>
+    <t>2026-10-13T08:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
